--- a/docs/ERP_Sheet_Plantilla.xlsx
+++ b/docs/ERP_Sheet_Plantilla.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -583,55 +583,69 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>- Los porcentajes (iva_pct, comision_default_pct) van como fraccion: 0.19 = 19%, 0 = exento.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>- Los precios en PRECIOS_PRODUCTO incluyen IVA (precio final al publico).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Pestanas incluidas (20, agrupadas por modulo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>- Configuracion: EMPRESA, USUARIOS, ROLES, PERMISOS_ROL</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>- Catalogo y precios: LINEAS, PRODUCTOS, LISTAS_PRECIO, PRECIOS_PRODUCTO</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>- Compras e inventario: PROVEEDORES, COMPRAS, COMPRAS_DETALLE, MOVIMIENTOS_INVENTARIO</t>
+          <t>- Configuracion: EMPRESA, USUARIOS, ROLES, PERMISOS_ROL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>- Ventas y cotizaciones: CLIENTES, COTIZACIONES, COTIZACIONES_DETALLE, VENTAS, VENTAS_DETALLE, COMISIONES</t>
+          <t>- Catalogo y precios: LINEAS, PRODUCTOS, LISTAS_PRECIO, PRECIOS_PRODUCTO</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>- Cartera: CXC, CXP</t>
+          <t>- Compras e inventario: PROVEEDORES, COMPRAS, COMPRAS_DETALLE, MOVIMIENTOS_INVENTARIO</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>- Ventas y cotizaciones: CLIENTES, COTIZACIONES, COTIZACIONES_DETALLE, VENTAS, VENTAS_DETALLE, COMISIONES</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>- Cartera: CXC, CXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Referencia completa del modelo de datos y los flujos: ver ERP-configurable-estructura.md en este mismo repo.</t>
         </is>
@@ -1852,14 +1866,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1880,10 +1895,15 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
+          <t>iva_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
           <t>costo_promedio</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>stock_actual</t>
         </is>
@@ -1906,9 +1926,12 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E2" s="5" t="n">
         <v>85000</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="F2" s="5" t="n">
         <v>20</v>
       </c>
     </row>

--- a/docs/ERP_Sheet_Plantilla.xlsx
+++ b/docs/ERP_Sheet_Plantilla.xlsx
@@ -9,25 +9,26 @@
   <sheets>
     <sheet name="LEEME" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="EMPRESA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="USUARIOS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ROLES" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="PERMISOS_ROL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="LINEAS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="PRODUCTOS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="LISTAS_PRECIO" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="PRECIOS_PRODUCTO" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="PROVEEDORES" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="COMPRAS" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="COMPRAS_DETALLE" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MOVIMIENTOS_INVENTARIO" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="CLIENTES" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="COTIZACIONES" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="COTIZACIONES_DETALLE" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="VENTAS" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="VENTAS_DETALLE" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="COMISIONES" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="CXC" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="CXP" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TASAS_CAMBIO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="USUARIOS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ROLES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PERMISOS_ROL" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="LINEAS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PRODUCTOS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="LISTAS_PRECIO" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="PRECIOS_PRODUCTO" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="PROVEEDORES" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="COMPRAS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="COMPRAS_DETALLE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="MOVIMIENTOS_INVENTARIO" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="CLIENTES" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="COTIZACIONES" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="COTIZACIONES_DETALLE" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="VENTAS" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="VENTAS_DETALLE" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="COMISIONES" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="CXC" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="CXP" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -597,55 +598,83 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>- moneda_base (EMPRESA) es la moneda en la que se llevan costo promedio, comisiones, CxC/CxP y reportes.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Pestanas incluidas (20, agrupadas por modulo)</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>- TASAS_CAMBIO trae la tasa vigente por moneda (cuantas unidades de moneda_base = 1 unidad de esa moneda).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>- Configuracion: EMPRESA, USUARIOS, ROLES, PERMISOS_ROL</t>
+          <t>- Al registrar una compra/venta en otra moneda, la tasa usada queda grabada en esa fila (moneda,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>- Catalogo y precios: LINEAS, PRODUCTOS, LISTAS_PRECIO, PRECIOS_PRODUCTO</t>
+          <t xml:space="preserve">  tasa_cambio): cambiar despues la tasa vigente en TASAS_CAMBIO NO altera compras/ventas ya registradas.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>- Compras e inventario: PROVEEDORES, COMPRAS, COMPRAS_DETALLE, MOVIMIENTOS_INVENTARIO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>- Ventas y cotizaciones: CLIENTES, COTIZACIONES, COTIZACIONES_DETALLE, VENTAS, VENTAS_DETALLE, COMISIONES</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Pestanas incluidas (21, agrupadas por modulo)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>- Cartera: CXC, CXP</t>
+          <t>- Configuracion: EMPRESA, USUARIOS, ROLES, PERMISOS_ROL, TASAS_CAMBIO</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>- Catalogo y precios: LINEAS, PRODUCTOS, LISTAS_PRECIO, PRECIOS_PRODUCTO</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>- Compras e inventario: PROVEEDORES, COMPRAS, COMPRAS_DETALLE, MOVIMIENTOS_INVENTARIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>- Ventas y cotizaciones: CLIENTES, COTIZACIONES, COTIZACIONES_DETALLE, VENTAS, VENTAS_DETALLE, COMISIONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>- Cartera: CXC, CXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Referencia completa del modelo de datos y los flujos: ver ERP-configurable-estructura.md en este mismo repo.</t>
         </is>
@@ -657,59 +686,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>contacto</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>prov-1</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Distribuidora Mascotas SAS</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>3009876543</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -732,40 +708,38 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>proveedor_id</t>
+          <t>producto_id</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>lista_id</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>estado</t>
+          <t>precio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>co-1</t>
+          <t>pp-1</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>prov-1</t>
+          <t>p-1</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>recibida</t>
-        </is>
+          <t>lp-1</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>120000</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +747,144 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>contacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>prov-1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Distribuidora Mascotas SAS</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>3009876543</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>proveedor_id</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>moneda</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>tasa_cambio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>co-1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>prov-1</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>01-08-2026</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>recibida</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -844,7 +955,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -948,7 +1059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1026,7 +1137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1101,7 +1212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1172,13 +1283,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1186,6 +1297,8 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1214,6 +1327,16 @@
           <t>estado</t>
         </is>
       </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>moneda</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>tasa_cambio</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -1240,6 +1363,14 @@
         <is>
           <t>cerrada</t>
         </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1247,7 +1378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1318,7 +1449,133 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>nit</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>logo_url</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>color_primario</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>color_secundario</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>direccion</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>telefono</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>moneda_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ej-1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Total Vet SAS</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>900123456-7</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>#2F5233</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>#F2A900</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Calle 10 # 5-20</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>3001234567</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>contacto@totalvet.com</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1372,194 +1629,6 @@
       <c r="D2" s="5" t="inlineStr">
         <is>
           <t>pendiente</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>nit</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>logo_url</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>color_primario</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>color_secundario</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>direccion</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>telefono</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>ej-1</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Total Vet SAS</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>900123456-7</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr"/>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>#2F5233</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>#F2A900</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Calle 10 # 5-20</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>3001234567</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>contacto@totalvet.com</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>cliente_id</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>venta_id</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>saldo</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>fecha_vencimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>cxc-1</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>cl-1</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>v-1</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>12-09-2026</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1661,12 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>proveedor_id</t>
+          <t>cliente_id</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>compra_id</t>
+          <t>venta_id</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
@@ -1614,25 +1683,25 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>cxp-1</t>
+          <t>cxc-1</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>prov-1</t>
+          <t>cl-1</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>co-1</t>
+          <t>v-1</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>800000</v>
+        <v>240000</v>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>12-09-2026</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1710,153 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>proveedor_id</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>compra_id</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>saldo</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>fecha_vencimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>cxp-1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>prov-1</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>co-1</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>moneda</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>tasa</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>fecha_actualizacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>tc-1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Dolar estadounidense</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>4100</v>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1714,7 +1929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1756,7 +1971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1809,7 +2024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1860,7 +2075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1940,48 +2155,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>lp-1</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Publico</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1999,33 +2172,35 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>producto_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>lista_id</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>precio</t>
+          <t>moneda</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>p-1</t>
+          <t>lp-1</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>lp-1</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>120000</v>
+          <t>Publico</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/ERP_Sheet_Plantilla.xlsx
+++ b/docs/ERP_Sheet_Plantilla.xlsx
@@ -29,6 +29,7 @@
     <sheet name="COMISIONES" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="CXC" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="CXP" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="PAGOS" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +632,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Pestanas incluidas (21, agrupadas por modulo)</t>
+          <t>Pestanas incluidas (22, agrupadas por modulo)</t>
         </is>
       </c>
     </row>
@@ -666,7 +667,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>- Cartera: CXC, CXP</t>
+          <t>- Cartera y caja: CXC, CXP, PAGOS</t>
         </is>
       </c>
     </row>
@@ -1783,6 +1784,79 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>referencia_tipo</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>referencia_id</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>monto</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>pag-1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>cxc</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>cxc-1</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>15-08-2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/ERP_Sheet_Plantilla.xlsx
+++ b/docs/ERP_Sheet_Plantilla.xlsx
@@ -787,12 +787,12 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Distribuidora Mascotas SAS</t>
+          <t>Proveedor Ejemplo SAS</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>3009876543</t>
+          <t>3000000001</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Veterinaria Amigo Fiel</t>
+          <t>Cliente Ejemplo</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>3011112222</t>
+          <t>3000000002</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Total Vet SAS</t>
+          <t>Mi Empresa SAS</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>900123456-7</t>
+          <t>900000000-0</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr"/>
@@ -1552,17 +1552,17 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Calle 10 # 5-20</t>
+          <t>Calle 1 # 2-34</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>3001234567</t>
+          <t>3000000000</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>contacto@totalvet.com</t>
+          <t>contacto@miempresa.com</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>admin@totalvet.com</t>
+          <t>admin@miempresa.com</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Alimento para mascotas</t>
+          <t>Línea Ejemplo</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Concentrado Perro Adulto 15kg</t>
+          <t>Producto Ejemplo</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
